--- a/data/trans_dic/IP16_n_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 52,14</t>
+          <t>17,59; 49,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 37,21</t>
+          <t>10,88; 36,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,84</t>
+          <t>0,0; 15,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 37,56</t>
+          <t>0,0; 36,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,06; 50,15</t>
+          <t>16,26; 51,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 25,28</t>
+          <t>3,18; 25,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,38</t>
+          <t>0,0; 49,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,91; 59,32</t>
+          <t>15,13; 58,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 43,56</t>
+          <t>21,75; 44,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 26,99</t>
+          <t>8,77; 26,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 21,79</t>
+          <t>2,25; 19,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,21; 42,04</t>
+          <t>11,44; 42,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,46; 51,13</t>
+          <t>34,03; 52,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,47; 26,82</t>
+          <t>12,92; 27,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 19,89</t>
+          <t>8,37; 20,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,74; 37,33</t>
+          <t>13,5; 37,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,01; 51,12</t>
+          <t>34,23; 50,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 20,97</t>
+          <t>9,0; 20,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 22,1</t>
+          <t>9,74; 21,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,56; 42,08</t>
+          <t>28,01; 42,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 48,44</t>
+          <t>36,01; 48,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,18; 21,43</t>
+          <t>12,52; 21,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 19,29</t>
+          <t>10,17; 19,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,82; 37,23</t>
+          <t>19,66; 37,21</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,69; 47,28</t>
+          <t>14,47; 44,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 25,01</t>
+          <t>5,81; 25,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 30,25</t>
+          <t>6,62; 28,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,44; 52,16</t>
+          <t>28,26; 52,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,12; 54,73</t>
+          <t>27,79; 54,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 26,63</t>
+          <t>6,12; 24,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 20,33</t>
+          <t>2,38; 21,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 43,41</t>
+          <t>18,13; 44,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 45,18</t>
+          <t>26,37; 45,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 21,42</t>
+          <t>7,86; 21,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 20,16</t>
+          <t>5,98; 20,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,57; 43,38</t>
+          <t>26,17; 44,28</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,2; 45,46</t>
+          <t>31,69; 45,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 24,09</t>
+          <t>12,8; 23,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,99</t>
+          <t>8,15; 17,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,74; 36,68</t>
+          <t>17,21; 36,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,97; 46,88</t>
+          <t>33,82; 46,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 18,56</t>
+          <t>9,66; 19,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,58</t>
+          <t>9,32; 19,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 40,25</t>
+          <t>27,46; 39,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,24; 44,21</t>
+          <t>34,04; 44,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 19,5</t>
+          <t>12,31; 19,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,16</t>
+          <t>10,05; 16,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,05; 35,86</t>
+          <t>23,89; 36,22</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4453; 11495</t>
+          <t>3878; 10981</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2468; 8582</t>
+          <t>2509; 8519</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2956</t>
+          <t>0; 2449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>276; 5720</t>
+          <t>0; 5583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3253; 10159</t>
+          <t>3295; 10472</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>552; 4578</t>
+          <t>576; 4535</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4162</t>
+          <t>0; 4383</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2650; 9294</t>
+          <t>2371; 9202</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9004; 18430</t>
+          <t>9203; 18856</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3648; 11111</t>
+          <t>3609; 11064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>558; 5332</t>
+          <t>551; 4850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3156; 12988</t>
+          <t>3534; 13163</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27002; 41265</t>
+          <t>27462; 42367</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11004; 23668</t>
+          <t>11404; 24046</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7273; 16501</t>
+          <t>6948; 17121</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15399; 45110</t>
+          <t>16312; 45101</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29814; 44819</t>
+          <t>30008; 44692</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9362; 21190</t>
+          <t>9098; 20739</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8276; 18924</t>
+          <t>8343; 18575</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33077; 50501</t>
+          <t>33621; 51374</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61236; 81555</t>
+          <t>60633; 81743</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23051; 40560</t>
+          <t>23692; 41527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17564; 32524</t>
+          <t>17154; 32378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50156; 89682</t>
+          <t>47365; 89624</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3538; 10663</t>
+          <t>3263; 9949</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2023; 9106</t>
+          <t>2117; 9270</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1967; 8709</t>
+          <t>1906; 8306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11426; 21719</t>
+          <t>11767; 21719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9916; 19300</t>
+          <t>9800; 19174</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2338; 10502</t>
+          <t>2415; 9854</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>633; 5869</t>
+          <t>688; 6220</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8503; 20190</t>
+          <t>8431; 20833</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14854; 26122</t>
+          <t>15244; 26544</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6134; 16248</t>
+          <t>5959; 16258</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3498; 11623</t>
+          <t>3448; 11723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22538; 38240</t>
+          <t>23071; 39034</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39093; 56965</t>
+          <t>39714; 57125</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19656; 35575</t>
+          <t>18904; 35340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11295; 22928</t>
+          <t>10393; 22664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29750; 65193</t>
+          <t>30581; 64467</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48642; 67125</t>
+          <t>48434; 66155</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15011; 29427</t>
+          <t>15323; 30154</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11687; 24135</t>
+          <t>11485; 24391</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49952; 73332</t>
+          <t>50027; 72760</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91926; 118712</t>
+          <t>91403; 118594</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36973; 59728</t>
+          <t>37709; 60077</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25228; 43032</t>
+          <t>25200; 42264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86563; 129050</t>
+          <t>85984; 130359</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16_n_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39,46%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21,91%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 49,81</t>
+          <t>17,2; 49,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 36,94</t>
+          <t>3,19; 28,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,61</t>
+          <t>0,0; 49,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,66</t>
+          <t>16,55; 61,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 51,69</t>
+          <t>18,03; 52,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 25,05</t>
+          <t>10,84; 37,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,89</t>
+          <t>0,0; 16,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 58,73</t>
+          <t>6,34; 49,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,75; 44,57</t>
+          <t>21,48; 44,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 26,88</t>
+          <t>9,05; 28,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 19,81</t>
+          <t>2,19; 21,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 42,6</t>
+          <t>16,88; 49,32</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>42,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>18,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>42,09%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,03; 52,49</t>
+          <t>34,38; 50,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 27,25</t>
+          <t>9,52; 21,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 20,63</t>
+          <t>9,11; 22,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 37,32</t>
+          <t>27,36; 43,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,23; 50,98</t>
+          <t>33,87; 50,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 20,53</t>
+          <t>12,23; 27,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 21,7</t>
+          <t>8,27; 20,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,01; 42,8</t>
+          <t>26,13; 41,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,01; 48,55</t>
+          <t>36,58; 48,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 21,94</t>
+          <t>12,06; 20,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 19,2</t>
+          <t>10,48; 19,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 37,21</t>
+          <t>28,69; 40,22</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39,99%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30,43%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>28,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,28%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14,64%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>39,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 44,12</t>
+          <t>26,37; 53,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 25,46</t>
+          <t>6,75; 26,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 28,85</t>
+          <t>2,26; 20,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,26; 52,16</t>
+          <t>18,93; 43,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,79; 54,37</t>
+          <t>14,77; 43,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 24,99</t>
+          <t>6,35; 25,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 21,55</t>
+          <t>6,01; 29,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 44,79</t>
+          <t>28,37; 53,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,37; 45,91</t>
+          <t>25,75; 45,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 21,44</t>
+          <t>7,33; 21,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 20,33</t>
+          <t>6,25; 20,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,17; 44,28</t>
+          <t>26,38; 45,01</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39,99%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>38,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,69; 45,59</t>
+          <t>33,6; 46,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,93</t>
+          <t>9,62; 18,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 17,78</t>
+          <t>9,34; 19,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 36,28</t>
+          <t>27,97; 40,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,82; 46,2</t>
+          <t>31,22; 45,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 19,02</t>
+          <t>13,13; 23,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 19,79</t>
+          <t>8,02; 17,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,46; 39,93</t>
+          <t>28,14; 40,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,04; 44,17</t>
+          <t>34,53; 44,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 19,62</t>
+          <t>12,48; 19,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,86</t>
+          <t>9,91; 17,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,89; 36,22</t>
+          <t>30,27; 39,25</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7342</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5053</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2265</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1814</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>7539</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3878; 10981</t>
+          <t>3484; 10102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2509; 8519</t>
+          <t>578; 5172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2449</t>
+          <t>0; 4314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5583</t>
+          <t>2304; 8548</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3295; 10472</t>
+          <t>3974; 11483</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>576; 4535</t>
+          <t>2499; 8544</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4383</t>
+          <t>0; 2590</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2371; 9202</t>
+          <t>620; 4863</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9203; 18856</t>
+          <t>9086; 18877</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3609; 11064</t>
+          <t>3727; 11567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>551; 4850</t>
+          <t>536; 5255</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3534; 13163</t>
+          <t>4000; 11690</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36904</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14427</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12958</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37341</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>34240</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16584</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11209</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32199</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36904</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14427</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12958</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>68527</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27462; 42367</t>
+          <t>30140; 44537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11404; 24046</t>
+          <t>9620; 21834</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6948; 17121</t>
+          <t>7798; 19041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16312; 45101</t>
+          <t>29524; 46636</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30008; 44692</t>
+          <t>27332; 41106</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9098; 20739</t>
+          <t>10792; 24381</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8343; 18575</t>
+          <t>6863; 16599</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33621; 51374</t>
+          <t>24222; 38828</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60633; 81743</t>
+          <t>61594; 81322</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23692; 41527</t>
+          <t>22819; 39071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17154; 32378</t>
+          <t>17672; 32175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47365; 89624</t>
+          <t>57545; 80683</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5603</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6354</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4833</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4216</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16199</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14103</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5603</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30158</t>
+          <t>29517</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3263; 9949</t>
+          <t>9300; 19031</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2117; 9270</t>
+          <t>2663; 10629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1906; 8306</t>
+          <t>652; 5784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11767; 21719</t>
+          <t>8162; 18882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9800; 19174</t>
+          <t>3331; 9755</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2415; 9854</t>
+          <t>2313; 9146</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>688; 6220</t>
+          <t>1730; 8444</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8431; 20833</t>
+          <t>11498; 21502</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15244; 26544</t>
+          <t>14890; 26279</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5959; 16258</t>
+          <t>5560; 16384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3448; 11723</t>
+          <t>3601; 11885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23071; 39034</t>
+          <t>22063; 37646</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57263</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>47937</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>26470</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>15989</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21844</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39714; 57125</t>
+          <t>48114; 67121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18904; 35340</t>
+          <t>15257; 30041</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10393; 22664</t>
+          <t>11520; 23909</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30581; 64467</t>
+          <t>46133; 66628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48434; 66155</t>
+          <t>39115; 57055</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15323; 30154</t>
+          <t>19392; 34820</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11485; 24391</t>
+          <t>10223; 22667</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50027; 72760</t>
+          <t>40244; 58311</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91403; 118594</t>
+          <t>92718; 118223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37709; 60077</t>
+          <t>38212; 60635</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25200; 42264</t>
+          <t>24849; 42911</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85984; 130359</t>
+          <t>93209; 120878</t>
         </is>
       </c>
     </row>
